--- a/data/out/variants/v4_no_fuel_consumption/summary_v4_no_fuel_consumption.xlsx
+++ b/data/out/variants/v4_no_fuel_consumption/summary_v4_no_fuel_consumption.xlsx
@@ -523,19 +523,19 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.3741651231492414</v>
+        <v>0.3741651231492448</v>
       </c>
       <c r="F2" t="n">
-        <v>225.0454611271984</v>
+        <v>225.0454611271971</v>
       </c>
       <c r="G2" t="n">
-        <v>157267.1502250699</v>
+        <v>157267.150225069</v>
       </c>
       <c r="H2" t="n">
-        <v>396.5692250100477</v>
+        <v>396.5692250100467</v>
       </c>
       <c r="I2" t="n">
-        <v>38.91858480332692</v>
+        <v>38.91858480332672</v>
       </c>
       <c r="J2" t="n">
         <v>48192</v>
@@ -547,7 +547,7 @@
         <v>9639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05123448371887207</v>
+        <v>0.02742719650268555</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.3741702717441713</v>
+        <v>0.3741706956679947</v>
       </c>
       <c r="F3" t="n">
-        <v>225.0371949644052</v>
+        <v>225.0368685500653</v>
       </c>
       <c r="G3" t="n">
-        <v>157265.8564255674</v>
+        <v>157265.749897002</v>
       </c>
       <c r="H3" t="n">
-        <v>396.5675937662676</v>
+        <v>396.5674594529939</v>
       </c>
       <c r="I3" t="n">
-        <v>38.91566535744706</v>
+        <v>38.91553270331269</v>
       </c>
       <c r="J3" t="n">
         <v>48192</v>
@@ -598,7 +598,7 @@
         <v>9639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04413223266601562</v>
+        <v>0.01509618759155273</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.3734423242246825</v>
+        <v>0.3735319579051222</v>
       </c>
       <c r="F4" t="n">
-        <v>222.7800866259209</v>
+        <v>222.6965894751962</v>
       </c>
       <c r="G4" t="n">
-        <v>157448.7836418956</v>
+        <v>157426.2594362172</v>
       </c>
       <c r="H4" t="n">
-        <v>396.7981648670967</v>
+        <v>396.7697814050576</v>
       </c>
       <c r="I4" t="n">
-        <v>38.07262062116765</v>
+        <v>38.05211565308698</v>
       </c>
       <c r="J4" t="n">
         <v>48192</v>
@@ -649,7 +649,7 @@
         <v>9639</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5561795234680176</v>
+        <v>0.2510144710540771</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3656778199039765</v>
+        <v>0.3657481237935583</v>
       </c>
       <c r="F5" t="n">
-        <v>225.9892370535047</v>
+        <v>225.973798676042</v>
       </c>
       <c r="G5" t="n">
-        <v>159399.9396298334</v>
+        <v>159382.2728413989</v>
       </c>
       <c r="H5" t="n">
-        <v>399.2492199489355</v>
+        <v>399.2270943227663</v>
       </c>
       <c r="I5" t="n">
-        <v>48.01837976629363</v>
+        <v>47.98441641969514</v>
       </c>
       <c r="J5" t="n">
         <v>48192</v>
@@ -704,7 +704,7 @@
         <v>9639</v>
       </c>
       <c r="M5" t="n">
-        <v>18.7397997379303</v>
+        <v>4.214031457901001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-173.742152063456</v>
+        <v>-173.6921312096436</v>
       </c>
     </row>
     <row r="6">
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2383008502142328</v>
+        <v>0.2383008502142329</v>
       </c>
       <c r="F6" t="n">
-        <v>238.8767359583285</v>
+        <v>238.8767359583283</v>
       </c>
       <c r="G6" t="n">
         <v>191408.723046019</v>
@@ -749,7 +749,7 @@
         <v>437.5028263291781</v>
       </c>
       <c r="I6" t="n">
-        <v>35.35258550619508</v>
+        <v>35.35258550619489</v>
       </c>
       <c r="J6" t="n">
         <v>48192</v>
@@ -761,7 +761,7 @@
         <v>9639</v>
       </c>
       <c r="M6" t="n">
-        <v>4.075842380523682</v>
+        <v>1.010054349899292</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-210.4604964458112</v>
+        <v>-211.3051925478418</v>
       </c>
     </row>
     <row r="7">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1766977764895312</v>
+        <v>0.1766977764895311</v>
       </c>
       <c r="F7" t="n">
-        <v>249.48828823018</v>
+        <v>249.4882882301801</v>
       </c>
       <c r="G7" t="n">
         <v>206889.0681148973</v>
@@ -818,7 +818,7 @@
         <v>9639</v>
       </c>
       <c r="M7" t="n">
-        <v>1193.006401538849</v>
+        <v>311.2376093864441</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-207.2169265150175</v>
+        <v>-207.6449515442118</v>
       </c>
     </row>
     <row r="8">
@@ -847,23 +847,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 3, 'n_estimators': 100}</t>
+          <t>{'learning_rate': 0.05, 'max_depth': 3, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-0.1625316015716038</v>
+        <v>-0.1124701904683469</v>
       </c>
       <c r="F8" t="n">
-        <v>316.4043402240891</v>
+        <v>307.7420547203067</v>
       </c>
       <c r="G8" t="n">
-        <v>292134.6169548027</v>
+        <v>279554.5966464549</v>
       </c>
       <c r="H8" t="n">
-        <v>540.494789017251</v>
+        <v>528.7292280992748</v>
       </c>
       <c r="I8" t="n">
-        <v>45.69367096854692</v>
+        <v>44.88731855454729</v>
       </c>
       <c r="J8" t="n">
         <v>48192</v>
@@ -875,7 +875,7 @@
         <v>9639</v>
       </c>
       <c r="M8" t="n">
-        <v>643.640777349472</v>
+        <v>220.0895640850067</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-184.3428016309788</v>
+        <v>-185.0718368752186</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1248060129189383</v>
+        <v>0.1090964112529568</v>
       </c>
       <c r="F9" t="n">
-        <v>290.7122461719385</v>
+        <v>295.859411142765</v>
       </c>
       <c r="G9" t="n">
-        <v>219929.0409236456</v>
+        <v>223876.7344392454</v>
       </c>
       <c r="H9" t="n">
-        <v>468.9659272523385</v>
+        <v>473.1561417114285</v>
       </c>
       <c r="I9" t="n">
-        <v>72.27837913524093</v>
+        <v>74.61171120910693</v>
       </c>
       <c r="J9" t="n">
         <v>48192</v>
@@ -932,7 +932,7 @@
         <v>9639</v>
       </c>
       <c r="M9" t="n">
-        <v>513.2454476356506</v>
+        <v>151.3343899250031</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-247.3340336289516</v>
+        <v>-246.0695180410189</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5066072442481755</v>
+        <v>0.4960778419559149</v>
       </c>
       <c r="F10" t="n">
-        <v>228.0457624531294</v>
+        <v>232.5648969217317</v>
       </c>
       <c r="G10" t="n">
-        <v>123985.5359759491</v>
+        <v>126631.4880526532</v>
       </c>
       <c r="H10" t="n">
-        <v>352.1157991001669</v>
+        <v>355.8531832830124</v>
       </c>
       <c r="I10" t="n">
-        <v>68.81673324551384</v>
+        <v>71.19059829156311</v>
       </c>
       <c r="J10" t="n">
         <v>48192</v>
@@ -989,7 +989,7 @@
         <v>9639</v>
       </c>
       <c r="M10" t="n">
-        <v>6.762314796447754</v>
+        <v>1.782235145568848</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-237.3289699323684</v>
+        <v>-237.8498150525132</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 801, 'learning_rate': 0.03541983595234932, 'max_depth': 3, 'subsample': 0.8507754699682213, 'colsample_bytree': 0.6549493139618847}</t>
+          <t>{'n_estimators': 997, 'learning_rate': 0.011382366428468103, 'max_depth': 3, 'subsample': 0.9607590276736878, 'colsample_bytree': 0.6283195517161019}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-0.07730651539236666</v>
+        <v>0.008300883771364953</v>
       </c>
       <c r="F11" t="n">
-        <v>308.2835644953601</v>
+        <v>287.3779260354587</v>
       </c>
       <c r="G11" t="n">
-        <v>270718.2547051628</v>
+        <v>249205.8203512196</v>
       </c>
       <c r="H11" t="n">
-        <v>520.3059241495938</v>
+        <v>499.2051886260995</v>
       </c>
       <c r="I11" t="n">
-        <v>50.79141406605141</v>
+        <v>44.83369550081007</v>
       </c>
       <c r="J11" t="n">
         <v>48192</v>
@@ -1046,7 +1046,7 @@
         <v>9639</v>
       </c>
       <c r="M11" t="n">
-        <v>136.3729155063629</v>
+        <v>67.09930205345154</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 389, 'learning_rate': 0.03224909033513408, 'num_leaves': 39, 'min_child_samples': 10}</t>
+          <t>{'n_estimators': 863, 'learning_rate': 0.012611146934564431, 'num_leaves': 32, 'min_child_samples': 33}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.04554541346774965</v>
+        <v>0.01656209793302299</v>
       </c>
       <c r="F12" t="n">
-        <v>276.1813485157831</v>
+        <v>282.244661261302</v>
       </c>
       <c r="G12" t="n">
-        <v>239846.5767815772</v>
+        <v>247129.8452711143</v>
       </c>
       <c r="H12" t="n">
-        <v>489.7413366069656</v>
+        <v>497.121559853437</v>
       </c>
       <c r="I12" t="n">
-        <v>42.20708441793835</v>
+        <v>42.79308480071787</v>
       </c>
       <c r="J12" t="n">
         <v>48192</v>
@@ -1101,7 +1101,7 @@
         <v>9639</v>
       </c>
       <c r="M12" t="n">
-        <v>349.6170012950897</v>
+        <v>126.5296831130981</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 449, 'learning_rate': 0.045836693527994715, 'depth': 4}</t>
+          <t>{'iterations': 419, 'learning_rate': 0.0321942840222264, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-0.004773684292309177</v>
+        <v>-0.09884887602305947</v>
       </c>
       <c r="F13" t="n">
-        <v>296.3764904470347</v>
+        <v>307.0434727312933</v>
       </c>
       <c r="G13" t="n">
-        <v>252491.351624492</v>
+        <v>276131.672510444</v>
       </c>
       <c r="H13" t="n">
-        <v>502.4851755270915</v>
+        <v>525.4823236898117</v>
       </c>
       <c r="I13" t="n">
-        <v>46.26477986873254</v>
+        <v>45.0119570589322</v>
       </c>
       <c r="J13" t="n">
         <v>48192</v>
@@ -1156,7 +1156,7 @@
         <v>9639</v>
       </c>
       <c r="M13" t="n">
-        <v>397.2723939418793</v>
+        <v>73.7200140953064</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 20, 'min_samples_split': 2, 'n_estimators': 300}</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2044112414671037</v>
+        <v>0.1538849872979617</v>
       </c>
       <c r="F14" t="n">
-        <v>263.264398259603</v>
+        <v>272.2198222455646</v>
       </c>
       <c r="G14" t="n">
-        <v>199924.9026119823</v>
+        <v>212621.7341543756</v>
       </c>
       <c r="H14" t="n">
-        <v>447.1296261846024</v>
+        <v>461.1092431890469</v>
       </c>
       <c r="I14" t="n">
-        <v>54.07014832808349</v>
+        <v>57.15196100856256</v>
       </c>
       <c r="J14" t="n">
         <v>48192</v>
@@ -1211,7 +1211,7 @@
         <v>9639</v>
       </c>
       <c r="M14" t="n">
-        <v>270.5005114078522</v>
+        <v>61.38380312919617</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-177.7205626115025</v>
+        <v>-176.9065472912322</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9639</v>
       </c>
       <c r="M15" t="n">
-        <v>42.29326462745667</v>
+        <v>12.08897423744202</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-194.5989665759903</v>
+        <v>-194.5988714599036</v>
       </c>
     </row>
     <row r="16">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.0001}</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.0001}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.3983266114888756</v>
+        <v>0.432871673541782</v>
       </c>
       <c r="F16" t="n">
-        <v>223.3968534471207</v>
+        <v>219.7548410249264</v>
       </c>
       <c r="G16" t="n">
-        <v>151195.5671974646</v>
+        <v>142514.677614022</v>
       </c>
       <c r="H16" t="n">
-        <v>388.838741893686</v>
+        <v>377.511162237651</v>
       </c>
       <c r="I16" t="n">
-        <v>41.60522000224093</v>
+        <v>47.52861857260295</v>
       </c>
       <c r="J16" t="n">
         <v>48192</v>
@@ -1325,7 +1325,7 @@
         <v>9639</v>
       </c>
       <c r="M16" t="n">
-        <v>4299.558969259262</v>
+        <v>3269.711710214615</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-167.3577540677307</v>
+        <v>-166.7903229421714</v>
       </c>
     </row>
   </sheetData>
